--- a/excel_data/TN SOLVE - NHÓM 1_7885627803068483682.xlsx
+++ b/excel_data/TN SOLVE - NHÓM 1_7885627803068483682.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-16T10:56:50.660615</t>
+          <t>2026-04-18T19:44:38.015556</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,11 @@
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -766,7 +770,11 @@
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="2" t="n">
@@ -809,12 +817,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Tuệ Nhi Có Pán Grok Nè</t>
+          <t>Tuệ Nhi Có Pán Grok</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Tuệ Nhi Có Pán Grok Nè</t>
+          <t>Tuệ Nhi Có Pán Grok</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1692,9 +1700,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="2" t="n">
@@ -1723,7 +1739,11 @@
       </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="45" customHeight="1">
       <c r="A46" s="2" t="n">
@@ -1750,9 +1770,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="45" customHeight="1">
       <c r="A47" s="2" t="n">
@@ -1779,9 +1807,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="45" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -1808,9 +1844,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="45" customHeight="1">
       <c r="A49" s="2" t="n">
@@ -1837,9 +1881,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="45" customHeight="1">
       <c r="A50" s="2" t="n">
@@ -1866,9 +1918,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="45" customHeight="1">
       <c r="A51" s="2" t="n">
@@ -1895,9 +1955,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="45" customHeight="1">
       <c r="A52" s="2" t="n">
@@ -1924,9 +1992,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="45" customHeight="1">
       <c r="A53" s="2" t="n">
@@ -1953,9 +2029,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="45" customHeight="1">
       <c r="A54" s="2" t="n">
@@ -1982,9 +2066,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="45" customHeight="1">
       <c r="A55" s="2" t="n">
@@ -2011,9 +2103,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="45" customHeight="1">
       <c r="A56" s="2" t="n">
@@ -2040,9 +2140,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="2" t="n">
@@ -2069,9 +2177,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="45" customHeight="1">
       <c r="A58" s="2" t="n">
@@ -2098,9 +2214,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="45" customHeight="1">
       <c r="A59" s="2" t="n">
@@ -2127,9 +2251,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="45" customHeight="1">
       <c r="A60" s="2" t="n">
@@ -2156,9 +2288,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="45" customHeight="1">
       <c r="A61" s="2" t="n">
@@ -2185,9 +2325,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="45" customHeight="1">
       <c r="A62" s="2" t="n">
@@ -2214,9 +2362,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="45" customHeight="1">
       <c r="A63" s="2" t="n">
@@ -2243,9 +2399,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="45" customHeight="1">
       <c r="A64" s="2" t="n">
@@ -2274,7 +2438,11 @@
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="45" customHeight="1">
       <c r="A65" s="2" t="n">
@@ -4043,7 +4211,11 @@
       </c>
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="45" customHeight="1">
       <c r="A126" s="2" t="n">
@@ -4072,7 +4244,11 @@
       </c>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
-      <c r="I126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="45" customHeight="1">
       <c r="A127" s="2" t="n">
@@ -4101,7 +4277,11 @@
       </c>
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="45" customHeight="1">
       <c r="A128" s="2" t="n">
@@ -4130,7 +4310,11 @@
       </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="45" customHeight="1">
       <c r="A129" s="2" t="n">
@@ -4188,7 +4372,11 @@
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="45" customHeight="1">
       <c r="A131" s="2" t="n">
@@ -6450,7 +6638,11 @@
       </c>
       <c r="G208" s="2" t="inlineStr"/>
       <c r="H208" s="2" t="inlineStr"/>
-      <c r="I208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="45" customHeight="1">
       <c r="A209" s="2" t="n">
@@ -6479,7 +6671,11 @@
       </c>
       <c r="G209" s="2" t="inlineStr"/>
       <c r="H209" s="2" t="inlineStr"/>
-      <c r="I209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="45" customHeight="1">
       <c r="A210" s="2" t="n">
@@ -6506,9 +6702,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H210" s="2" t="inlineStr"/>
-      <c r="I210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="45" customHeight="1">
       <c r="A211" s="2" t="n">
@@ -6535,9 +6739,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H211" s="2" t="inlineStr"/>
-      <c r="I211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="45" customHeight="1">
       <c r="A212" s="2" t="n">
@@ -6566,7 +6778,11 @@
       </c>
       <c r="G212" s="2" t="inlineStr"/>
       <c r="H212" s="2" t="inlineStr"/>
-      <c r="I212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="45" customHeight="1">
       <c r="A213" s="2" t="n">
@@ -6593,9 +6809,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H213" s="2" t="inlineStr"/>
-      <c r="I213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="45" customHeight="1">
       <c r="A214" s="2" t="n">
@@ -6622,9 +6846,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H214" s="2" t="inlineStr"/>
-      <c r="I214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="45" customHeight="1">
       <c r="A215" s="2" t="n">
@@ -6651,9 +6883,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H215" s="2" t="inlineStr"/>
-      <c r="I215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="45" customHeight="1">
       <c r="A216" s="2" t="n">
@@ -6680,9 +6920,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H216" s="2" t="inlineStr"/>
-      <c r="I216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="45" customHeight="1">
       <c r="A217" s="2" t="n">
@@ -6709,9 +6957,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H217" s="2" t="inlineStr"/>
-      <c r="I217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="45" customHeight="1">
       <c r="A218" s="2" t="n">
@@ -6738,9 +6994,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H218" s="2" t="inlineStr"/>
-      <c r="I218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="45" customHeight="1">
       <c r="A219" s="2" t="n">
@@ -6767,9 +7031,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H219" s="2" t="inlineStr"/>
-      <c r="I219" s="2" t="inlineStr"/>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="45" customHeight="1">
       <c r="A220" s="2" t="n">
@@ -6796,9 +7068,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H220" s="2" t="inlineStr"/>
-      <c r="I220" s="2" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="45" customHeight="1">
       <c r="A221" s="2" t="n">
@@ -6827,7 +7107,11 @@
       </c>
       <c r="G221" s="2" t="inlineStr"/>
       <c r="H221" s="2" t="inlineStr"/>
-      <c r="I221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="45" customHeight="1">
       <c r="A222" s="2" t="n">
@@ -6856,7 +7140,11 @@
       </c>
       <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr"/>
-      <c r="I222" s="2" t="inlineStr"/>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="45" customHeight="1">
       <c r="A223" s="2" t="n">
@@ -6885,7 +7173,11 @@
       </c>
       <c r="G223" s="2" t="inlineStr"/>
       <c r="H223" s="2" t="inlineStr"/>
-      <c r="I223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="45" customHeight="1">
       <c r="A224" s="2" t="n">
@@ -6914,7 +7206,11 @@
       </c>
       <c r="G224" s="2" t="inlineStr"/>
       <c r="H224" s="2" t="inlineStr"/>
-      <c r="I224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="45" customHeight="1">
       <c r="A225" s="2" t="n">
@@ -6943,7 +7239,11 @@
       </c>
       <c r="G225" s="2" t="inlineStr"/>
       <c r="H225" s="2" t="inlineStr"/>
-      <c r="I225" s="2" t="inlineStr"/>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="45" customHeight="1">
       <c r="A226" s="2" t="n">
@@ -6972,7 +7272,11 @@
       </c>
       <c r="G226" s="2" t="inlineStr"/>
       <c r="H226" s="2" t="inlineStr"/>
-      <c r="I226" s="2" t="inlineStr"/>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="45" customHeight="1">
       <c r="A227" s="2" t="n">
@@ -7001,7 +7305,11 @@
       </c>
       <c r="G227" s="2" t="inlineStr"/>
       <c r="H227" s="2" t="inlineStr"/>
-      <c r="I227" s="2" t="inlineStr"/>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="45" customHeight="1">
       <c r="A228" s="2" t="n">
@@ -7030,7 +7338,11 @@
       </c>
       <c r="G228" s="2" t="inlineStr"/>
       <c r="H228" s="2" t="inlineStr"/>
-      <c r="I228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="45" customHeight="1">
       <c r="A229" s="2" t="n">
@@ -7059,7 +7371,11 @@
       </c>
       <c r="G229" s="2" t="inlineStr"/>
       <c r="H229" s="2" t="inlineStr"/>
-      <c r="I229" s="2" t="inlineStr"/>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="45" customHeight="1">
       <c r="A230" s="2" t="n">
@@ -7088,7 +7404,11 @@
       </c>
       <c r="G230" s="2" t="inlineStr"/>
       <c r="H230" s="2" t="inlineStr"/>
-      <c r="I230" s="2" t="inlineStr"/>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="45" customHeight="1">
       <c r="A231" s="2" t="n">
@@ -7117,7 +7437,11 @@
       </c>
       <c r="G231" s="2" t="inlineStr"/>
       <c r="H231" s="2" t="inlineStr"/>
-      <c r="I231" s="2" t="inlineStr"/>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="45" customHeight="1">
       <c r="A232" s="2" t="n">
@@ -7146,7 +7470,11 @@
       </c>
       <c r="G232" s="2" t="inlineStr"/>
       <c r="H232" s="2" t="inlineStr"/>
-      <c r="I232" s="2" t="inlineStr"/>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="45" customHeight="1">
       <c r="A233" s="2" t="n">
@@ -7175,7 +7503,11 @@
       </c>
       <c r="G233" s="2" t="inlineStr"/>
       <c r="H233" s="2" t="inlineStr"/>
-      <c r="I233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="45" customHeight="1">
       <c r="A234" s="2" t="n">
@@ -7204,7 +7536,11 @@
       </c>
       <c r="G234" s="2" t="inlineStr"/>
       <c r="H234" s="2" t="inlineStr"/>
-      <c r="I234" s="2" t="inlineStr"/>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="45" customHeight="1">
       <c r="A235" s="2" t="n">
@@ -7233,7 +7569,11 @@
       </c>
       <c r="G235" s="2" t="inlineStr"/>
       <c r="H235" s="2" t="inlineStr"/>
-      <c r="I235" s="2" t="inlineStr"/>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="45" customHeight="1">
       <c r="A236" s="2" t="n">
@@ -7262,7 +7602,11 @@
       </c>
       <c r="G236" s="2" t="inlineStr"/>
       <c r="H236" s="2" t="inlineStr"/>
-      <c r="I236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="45" customHeight="1">
       <c r="A237" s="2" t="n">
@@ -7291,7 +7635,11 @@
       </c>
       <c r="G237" s="2" t="inlineStr"/>
       <c r="H237" s="2" t="inlineStr"/>
-      <c r="I237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="45" customHeight="1">
       <c r="A238" s="2" t="n">
@@ -7378,7 +7726,11 @@
       </c>
       <c r="G240" s="2" t="inlineStr"/>
       <c r="H240" s="2" t="inlineStr"/>
-      <c r="I240" s="2" t="inlineStr"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="45" customHeight="1">
       <c r="A241" s="2" t="n">
@@ -7407,7 +7759,11 @@
       </c>
       <c r="G241" s="2" t="inlineStr"/>
       <c r="H241" s="2" t="inlineStr"/>
-      <c r="I241" s="2" t="inlineStr"/>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="45" customHeight="1">
       <c r="A242" s="2" t="n">
@@ -7465,7 +7821,11 @@
       </c>
       <c r="G243" s="2" t="inlineStr"/>
       <c r="H243" s="2" t="inlineStr"/>
-      <c r="I243" s="2" t="inlineStr"/>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="45" customHeight="1">
       <c r="A244" s="2" t="n">
@@ -7494,7 +7854,11 @@
       </c>
       <c r="G244" s="2" t="inlineStr"/>
       <c r="H244" s="2" t="inlineStr"/>
-      <c r="I244" s="2" t="inlineStr"/>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="45" customHeight="1">
       <c r="A245" s="2" t="n">
@@ -7523,7 +7887,11 @@
       </c>
       <c r="G245" s="2" t="inlineStr"/>
       <c r="H245" s="2" t="inlineStr"/>
-      <c r="I245" s="2" t="inlineStr"/>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="45" customHeight="1">
       <c r="A246" s="2" t="n">
@@ -8103,7 +8471,11 @@
       </c>
       <c r="G265" s="2" t="inlineStr"/>
       <c r="H265" s="2" t="inlineStr"/>
-      <c r="I265" s="2" t="inlineStr"/>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="45" customHeight="1">
       <c r="A266" s="2" t="n">
@@ -8132,7 +8504,11 @@
       </c>
       <c r="G266" s="2" t="inlineStr"/>
       <c r="H266" s="2" t="inlineStr"/>
-      <c r="I266" s="2" t="inlineStr"/>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="45" customHeight="1">
       <c r="A267" s="2" t="n">
@@ -8161,7 +8537,11 @@
       </c>
       <c r="G267" s="2" t="inlineStr"/>
       <c r="H267" s="2" t="inlineStr"/>
-      <c r="I267" s="2" t="inlineStr"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="45" customHeight="1">
       <c r="A268" s="2" t="n">
@@ -8190,7 +8570,11 @@
       </c>
       <c r="G268" s="2" t="inlineStr"/>
       <c r="H268" s="2" t="inlineStr"/>
-      <c r="I268" s="2" t="inlineStr"/>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="45" customHeight="1">
       <c r="A269" s="2" t="n">
@@ -8219,7 +8603,11 @@
       </c>
       <c r="G269" s="2" t="inlineStr"/>
       <c r="H269" s="2" t="inlineStr"/>
-      <c r="I269" s="2" t="inlineStr"/>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="45" customHeight="1">
       <c r="A270" s="2" t="n">
@@ -8248,7 +8636,11 @@
       </c>
       <c r="G270" s="2" t="inlineStr"/>
       <c r="H270" s="2" t="inlineStr"/>
-      <c r="I270" s="2" t="inlineStr"/>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="45" customHeight="1">
       <c r="A271" s="2" t="n">
@@ -8277,7 +8669,11 @@
       </c>
       <c r="G271" s="2" t="inlineStr"/>
       <c r="H271" s="2" t="inlineStr"/>
-      <c r="I271" s="2" t="inlineStr"/>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="45" customHeight="1">
       <c r="A272" s="2" t="n">
@@ -8306,7 +8702,11 @@
       </c>
       <c r="G272" s="2" t="inlineStr"/>
       <c r="H272" s="2" t="inlineStr"/>
-      <c r="I272" s="2" t="inlineStr"/>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="45" customHeight="1">
       <c r="A273" s="2" t="n">
@@ -8335,7 +8735,11 @@
       </c>
       <c r="G273" s="2" t="inlineStr"/>
       <c r="H273" s="2" t="inlineStr"/>
-      <c r="I273" s="2" t="inlineStr"/>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="45" customHeight="1">
       <c r="A274" s="2" t="n">
@@ -8364,7 +8768,11 @@
       </c>
       <c r="G274" s="2" t="inlineStr"/>
       <c r="H274" s="2" t="inlineStr"/>
-      <c r="I274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="45" customHeight="1">
       <c r="A275" s="2" t="n">
@@ -8393,7 +8801,11 @@
       </c>
       <c r="G275" s="2" t="inlineStr"/>
       <c r="H275" s="2" t="inlineStr"/>
-      <c r="I275" s="2" t="inlineStr"/>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="45" customHeight="1">
       <c r="A276" s="2" t="n">
@@ -8422,7 +8834,11 @@
       </c>
       <c r="G276" s="2" t="inlineStr"/>
       <c r="H276" s="2" t="inlineStr"/>
-      <c r="I276" s="2" t="inlineStr"/>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="45" customHeight="1">
       <c r="A277" s="2" t="n">
@@ -8451,7 +8867,11 @@
       </c>
       <c r="G277" s="2" t="inlineStr"/>
       <c r="H277" s="2" t="inlineStr"/>
-      <c r="I277" s="2" t="inlineStr"/>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="45" customHeight="1">
       <c r="A278" s="2" t="n">
